--- a/packages/shared/src/tally/fixtures/sharma-vouchers.xlsx
+++ b/packages/shared/src/tally/fixtures/sharma-vouchers.xlsx
@@ -6,7 +6,9 @@
     <sheet name="Credit Note" sheetId="2" r:id="rId2"/>
     <sheet name="Debit Note" sheetId="3" r:id="rId3"/>
     <sheet name="Receipt" sheetId="4" r:id="rId4"/>
-    <sheet name="Ledgers" sheetId="5" r:id="rId5"/>
+    <sheet name="Payment" sheetId="5" r:id="rId5"/>
+    <sheet name="Journal" sheetId="6" r:id="rId6"/>
+    <sheet name="Ledgers" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -11375,6 +11377,559 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="7" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="40" customWidth="1"/>
+    <col min="15" max="15" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voucher Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voucher No</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancelled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Party Ledger</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Party GSTIN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of Supply</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Against</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ledger</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSN</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate %</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credit</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bills</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Narration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMPR/26-27/00001</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lakshmi Interiors</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36ABCPL5521Q1ZC</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMPA/26-27/00001 (2026-09-13)</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lakshmi Interiors</t>
+        </is>
+      </c>
+      <c r="L2" s="3">
+        <v>5000.00</v>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agst Ref AMPA/26-27/00001 5000.00</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refund AMPR/26-27/00001 by UPI; against receipt AMPA/26-27/00001 dated 13-09-2026; ref UTR 626711230045; Order reduced: two rooms dropped; [paint:rf-001]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMPR/26-27/00001</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lakshmi Interiors</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36ABCPL5521Q1ZC</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMPA/26-27/00001 (2026-09-13)</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UPI Clearing</t>
+        </is>
+      </c>
+      <c r="M3" s="3">
+        <v>5000.00</v>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refund AMPR/26-27/00001 by UPI; against receipt AMPA/26-27/00001 dated 13-09-2026; ref UTR 626711230045; Order reduced: two rooms dropped; [paint:rf-001]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000885</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sri Sai Constructions</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36AAMFS7310K1ZV</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000878 (2026-09-06)</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sri Sai Constructions</t>
+        </is>
+      </c>
+      <c r="L4" s="3">
+        <v>4000.00</v>
+      </c>
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On Account 4000.00</t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refund RC-000885 by NEFT / RTGS; against receipt RC-000878 dated 06-09-2026; ref NEFT HDFCN26269004411; [paint:rf-002]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000885</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sri Sai Constructions</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36AAMFS7310K1ZV</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000878 (2026-09-06)</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDFC Bank</t>
+        </is>
+      </c>
+      <c r="M5" s="3">
+        <v>4000.00</v>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refund RC-000885 by NEFT / RTGS; against receipt RC-000878 dated 06-09-2026; ref NEFT HDFCN26269004411; [paint:rf-002]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="7" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="40" customWidth="1"/>
+    <col min="15" max="15" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voucher Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voucher No</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancelled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Party Ledger</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Party GSTIN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of Supply</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Against</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ledger</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSN</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate %</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credit</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bills</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Narration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Journal</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000880/BOUNCE</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vijayawada Builders Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37AADCV8890H1ZP</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000880 (2026-09-15)</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vijayawada Builders Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L2" s="3">
+        <v>100500.00</v>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agst Ref AMP/26-27/000414 95900.00; On Account 4100.00; New Ref RC-000880/BOUNCE 500.00</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cheque bounced: receipt RC-000880 dated 15-09-2026 by Cheque; ref Cheque 118870, Andhra Bank; Funds insufficient; bounce charge Rs 500.00; [paint:rc-011-bounce]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Journal</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000880/BOUNCE</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vijayawada Builders Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37AADCV8890H1ZP</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000880 (2026-09-15)</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cheques in Hand</t>
+        </is>
+      </c>
+      <c r="M3" s="3">
+        <v>100000.00</v>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cheque bounced: receipt RC-000880 dated 15-09-2026 by Cheque; ref Cheque 118870, Andhra Bank; Funds insufficient; bounce charge Rs 500.00; [paint:rc-011-bounce]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Journal</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000880/BOUNCE</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vijayawada Builders Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37AADCV8890H1ZP</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-000880 (2026-09-15)</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cheque Bounce Charges</t>
+        </is>
+      </c>
+      <c r="M4" s="3">
+        <v>500.00</v>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cheque bounced: receipt RC-000880 dated 15-09-2026 by Cheque; ref Cheque 118870, Andhra Bank; Funds insufficient; bounce charge Rs 500.00; [paint:rc-011-bounce]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
@@ -11505,12 +12060,12 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cheques in Hand</t>
+          <t xml:space="preserve">Cheque Bounce Charges</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Assets</t>
+          <t xml:space="preserve">Indirect Incomes</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -11519,21 +12074,21 @@
         </is>
       </c>
       <c r="H5" s="3">
-        <v>210000.00</v>
+        <v>0.00</v>
       </c>
       <c r="I5" s="3">
-        <v>0.00</v>
+        <v>500.00</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">HDFC Bank</t>
+          <t xml:space="preserve">Cheques in Hand</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank Accounts</t>
+          <t xml:space="preserve">Current Assets</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -11542,82 +12097,72 @@
         </is>
       </c>
       <c r="H6" s="3">
-        <v>35925.00</v>
+        <v>210000.00</v>
       </c>
       <c r="I6" s="3">
-        <v>0.00</v>
+        <v>100000.00</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lakshmi Interiors</t>
+          <t xml:space="preserve">HDFC Bank</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundry Debtors</t>
+          <t xml:space="preserve">Bank Accounts</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36ABCPL5521Q1ZC</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telangana</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="H7" s="3">
-        <v>95770.00</v>
+        <v>35925.00</v>
       </c>
       <c r="I7" s="3">
-        <v>85000.00</v>
+        <v>4000.00</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Output CGST 9%</t>
+          <t xml:space="preserve">Lakshmi Interiors</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duties &amp; Taxes</t>
+          <t xml:space="preserve">Sundry Debtors</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CGST</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36ABCPL5521Q1ZC</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telangana</t>
         </is>
       </c>
       <c r="H8" s="3">
-        <v>835.17</v>
+        <v>100770.00</v>
       </c>
       <c r="I8" s="3">
-        <v>39204.95</v>
+        <v>85000.00</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Output IGST 18%</t>
+          <t xml:space="preserve">Output CGST 9%</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
@@ -11632,25 +12177,25 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">IGST</t>
+          <t xml:space="preserve">CGST</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H9" s="3">
-        <v>808.47</v>
+        <v>835.17</v>
       </c>
       <c r="I9" s="3">
-        <v>33635.60</v>
+        <v>39204.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Output SGST 9%</t>
+          <t xml:space="preserve">Output IGST 18%</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
@@ -11665,53 +12210,58 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SGST</t>
+          <t xml:space="preserve">IGST</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H10" s="3">
-        <v>835.17</v>
+        <v>808.47</v>
       </c>
       <c r="I10" s="3">
-        <v>39204.95</v>
+        <v>33635.60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravi Kumar (Painter)</t>
+          <t xml:space="preserve">Output SGST 9%</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundry Debtors</t>
+          <t xml:space="preserve">Duties &amp; Taxes</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telangana</t>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SGST</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H11" s="3">
-        <v>41000.00</v>
+        <v>835.17</v>
       </c>
       <c r="I11" s="3">
-        <v>3000.00</v>
+        <v>39204.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reddy &amp; Sons Contractors</t>
+          <t xml:space="preserve">Ravi Kumar (Painter)</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
@@ -11724,55 +12274,60 @@
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36AAJFR2264P1ZM</t>
-        </is>
-      </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Telangana</t>
         </is>
       </c>
       <c r="H12" s="3">
-        <v>176050.00</v>
+        <v>41000.00</v>
       </c>
       <c r="I12" s="3">
-        <v>75925.00</v>
+        <v>3000.00</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round Off</t>
+          <t xml:space="preserve">Reddy &amp; Sons Contractors</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indirect Expenses</t>
+          <t xml:space="preserve">Sundry Debtors</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36AAJFR2264P1ZM</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telangana</t>
         </is>
       </c>
       <c r="H13" s="3">
-        <v>0.28</v>
+        <v>176050.00</v>
       </c>
       <c r="I13" s="3">
-        <v>0.07</v>
+        <v>75925.00</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Exempt Interstate</t>
+          <t xml:space="preserve">Round Off</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Accounts</t>
+          <t xml:space="preserve">Indirect Expenses</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -11781,16 +12336,16 @@
         </is>
       </c>
       <c r="H14" s="3">
-        <v>0.00</v>
+        <v>0.28</v>
       </c>
       <c r="I14" s="3">
-        <v>100.00</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Exempt Local</t>
+          <t xml:space="preserve">Sales Exempt Interstate</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -11807,13 +12362,13 @@
         <v>0.00</v>
       </c>
       <c r="I15" s="3">
-        <v>150.00</v>
+        <v>100.00</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales GST 18% Interstate</t>
+          <t xml:space="preserve">Sales Exempt Local</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
@@ -11827,16 +12382,16 @@
         </is>
       </c>
       <c r="H16" s="3">
-        <v>4491.52</v>
+        <v>0.00</v>
       </c>
       <c r="I16" s="3">
-        <v>186864.43</v>
+        <v>150.00</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales GST 18% Local</t>
+          <t xml:space="preserve">Sales GST 18% Interstate</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
@@ -11850,49 +12405,39 @@
         </is>
       </c>
       <c r="H17" s="3">
-        <v>9279.66</v>
+        <v>4491.52</v>
       </c>
       <c r="I17" s="3">
-        <v>435610.27</v>
+        <v>186864.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sri Sai Constructions</t>
+          <t xml:space="preserve">Sales GST 18% Local</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundry Debtors</t>
+          <t xml:space="preserve">Sales Accounts</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36AAMFS7310K1ZV</t>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telangana</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="H18" s="3">
-        <v>153985.00</v>
+        <v>9279.66</v>
       </c>
       <c r="I18" s="3">
-        <v>59060.00</v>
+        <v>435610.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Srinivas Rao</t>
+          <t xml:space="preserve">Sri Sai Constructions</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
@@ -11905,71 +12450,104 @@
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36AAMFS7310K1ZV</t>
+        </is>
+      </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andhra Pradesh</t>
+          <t xml:space="preserve">Telangana</t>
         </is>
       </c>
       <c r="H19" s="3">
-        <v>11400.00</v>
+        <v>157985.00</v>
       </c>
       <c r="I19" s="3">
-        <v>11400.00</v>
+        <v>59060.00</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UPI Clearing</t>
+          <t xml:space="preserve">Srinivas Rao</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Assets</t>
+          <t xml:space="preserve">Sundry Debtors</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andhra Pradesh</t>
         </is>
       </c>
       <c r="H20" s="3">
-        <v>84635.00</v>
+        <v>11400.00</v>
       </c>
       <c r="I20" s="3">
-        <v>0.00</v>
+        <v>11400.00</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">UPI Clearing</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Assets</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="H21" s="3">
+        <v>84635.00</v>
+      </c>
+      <c r="I21" s="3">
+        <v>5000.00</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vijayawada Builders Pvt Ltd</t>
         </is>
       </c>
-      <c r="B21" s="0" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Sundry Debtors</t>
         </is>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="D21" s="0" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">37AADCV8890H1ZP</t>
         </is>
       </c>
-      <c r="E21" s="0" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Andhra Pradesh</t>
         </is>
       </c>
-      <c r="H21" s="3">
-        <v>209200.00</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="H22" s="3">
+        <v>309700.00</v>
+      </c>
+      <c r="I22" s="3">
         <v>105300.00</v>
       </c>
     </row>
